--- a/APLOS/POPResources/Templates/Lvr20181Bengali.xlsx
+++ b/APLOS/POPResources/Templates/Lvr20181Bengali.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Siddik 2018\Sadman\Compliance Info\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Aplos.New\APLOS\POPResources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF9247B-F3FB-46BB-8C49-D5CA1F4A27A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A8A106-21EC-449B-9F84-E58BC06EB4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -180,7 +180,7 @@
     <numFmt numFmtId="164" formatCode="[$-5000445]###0;"/>
     <numFmt numFmtId="165" formatCode="[$-5000445]#,##0_);\(#,##0\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,70 +500,70 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -577,9 +577,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -623,76 +620,67 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -719,13 +707,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>97194</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>272340</xdr:rowOff>
+      <xdr:rowOff>272341</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>933061</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>213829</xdr:rowOff>
+      <xdr:rowOff>62205</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -742,8 +730,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5569209" y="612519"/>
-          <a:ext cx="6657781" cy="582968"/>
+          <a:off x="5695561" y="614463"/>
+          <a:ext cx="6807459" cy="427456"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1152,254 +1140,254 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V47"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="2" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="36" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="36" customWidth="1"/>
-    <col min="4" max="6" width="9.140625" style="36" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="36" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" style="36" customWidth="1"/>
-    <col min="9" max="11" width="9.140625" style="36" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" style="36" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="37" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" style="37" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="37" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" style="37" customWidth="1"/>
-    <col min="17" max="19" width="9.85546875" style="36" customWidth="1"/>
-    <col min="20" max="20" width="15.28515625" style="36" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="36" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" style="36" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="36"/>
+    <col min="1" max="1" width="1.109375" style="2" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="35" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="35" customWidth="1"/>
+    <col min="4" max="6" width="9.109375" style="35" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" style="35" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" style="35" customWidth="1"/>
+    <col min="9" max="11" width="9.109375" style="35" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" style="35" customWidth="1"/>
+    <col min="13" max="13" width="13.5546875" style="36" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" style="36" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="36" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" style="36" customWidth="1"/>
+    <col min="17" max="19" width="9.88671875" style="35" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" style="35" customWidth="1"/>
+    <col min="21" max="21" width="14.33203125" style="35" customWidth="1"/>
+    <col min="22" max="22" width="15.88671875" style="35" customWidth="1"/>
+    <col min="23" max="16384" width="9.109375" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="61" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="63" t="s">
+    <row r="1" spans="1:22" s="43" customFormat="1" ht="27" customHeight="1">
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-    </row>
-    <row r="2" spans="1:22" s="2" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="62" t="s">
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+    </row>
+    <row r="2" spans="1:22" s="2" customFormat="1" ht="25.8">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-    </row>
-    <row r="3" spans="1:22" s="41" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="42" t="s">
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+    </row>
+    <row r="3" spans="1:22" s="39" customFormat="1" ht="24.9" customHeight="1">
+      <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="48" t="s">
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="49"/>
-      <c r="S3" s="56" t="s">
+      <c r="R3" s="52"/>
+      <c r="S3" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-    </row>
-    <row r="4" spans="1:22" s="41" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="42" t="s">
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="50"/>
+    </row>
+    <row r="4" spans="1:22" s="39" customFormat="1" ht="24.9" customHeight="1">
+      <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="48" t="s">
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="49"/>
-      <c r="S4" s="56" t="s">
+      <c r="R4" s="52"/>
+      <c r="S4" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-    </row>
-    <row r="5" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="60" t="s">
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
+      <c r="V4" s="50"/>
+    </row>
+    <row r="5" spans="1:22" s="2" customFormat="1">
+      <c r="B5" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="60"/>
-      <c r="U5" s="60"/>
-      <c r="V5" s="60"/>
-    </row>
-    <row r="6" spans="1:22" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="38" t="s">
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="54"/>
+      <c r="V5" s="54"/>
+    </row>
+    <row r="6" spans="1:22" s="1" customFormat="1" ht="27" customHeight="1">
+      <c r="A6" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="56"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="50" t="s">
+      <c r="H6" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="45" t="s">
+      <c r="I6" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="57" t="s">
+      <c r="J6" s="56"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="50" t="s">
+      <c r="M6" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="50" t="s">
+      <c r="N6" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="50" t="s">
+      <c r="O6" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="45" t="s">
+      <c r="Q6" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="46"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="52" t="s">
+      <c r="R6" s="56"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="U6" s="50" t="s">
+      <c r="U6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="V6" s="50" t="s">
+      <c r="V6" s="48" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="39" t="s">
+    <row r="7" spans="1:22" s="1" customFormat="1" ht="13.8">
+      <c r="A7" s="37"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="39" t="s">
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="40" t="s">
+      <c r="J7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="58"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="39" t="s">
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="R7" s="40" t="s">
+      <c r="R7" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="S7" s="40" t="s">
+      <c r="S7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="T7" s="53"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-    </row>
-    <row r="8" spans="1:22" s="9" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T7" s="59"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+    </row>
+    <row r="8" spans="1:22" s="9" customFormat="1" ht="24.9" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
@@ -1461,7 +1449,7 @@
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
     </row>
-    <row r="9" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
@@ -1485,7 +1473,7 @@
       <c r="U9" s="11"/>
       <c r="V9" s="15"/>
     </row>
-    <row r="10" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A10" s="17"/>
       <c r="B10" s="18"/>
       <c r="C10" s="19"/>
@@ -1509,7 +1497,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="22"/>
     </row>
-    <row r="11" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="18"/>
       <c r="C11" s="19"/>
@@ -1533,7 +1521,7 @@
       <c r="U11" s="18"/>
       <c r="V11" s="22"/>
     </row>
-    <row r="12" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="18"/>
       <c r="C12" s="19"/>
@@ -1557,7 +1545,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="22"/>
     </row>
-    <row r="13" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A13" s="17"/>
       <c r="B13" s="18"/>
       <c r="C13" s="19"/>
@@ -1581,7 +1569,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="22"/>
     </row>
-    <row r="14" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
@@ -1605,7 +1593,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="22"/>
     </row>
-    <row r="15" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A15" s="17"/>
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
@@ -1629,7 +1617,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="22"/>
     </row>
-    <row r="16" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A16" s="17"/>
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
@@ -1653,7 +1641,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="22"/>
     </row>
-    <row r="17" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
@@ -1677,7 +1665,7 @@
       <c r="U17" s="18"/>
       <c r="V17" s="22"/>
     </row>
-    <row r="18" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A18" s="17"/>
       <c r="B18" s="18"/>
       <c r="C18" s="19"/>
@@ -1701,7 +1689,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="22"/>
     </row>
-    <row r="19" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A19" s="17"/>
       <c r="B19" s="18"/>
       <c r="C19" s="19"/>
@@ -1725,7 +1713,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="22"/>
     </row>
-    <row r="20" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
@@ -1749,7 +1737,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="22"/>
     </row>
-    <row r="21" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A21" s="17"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
@@ -1773,7 +1761,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="22"/>
     </row>
-    <row r="22" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
@@ -1797,7 +1785,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="22"/>
     </row>
-    <row r="23" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A23" s="17"/>
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
@@ -1821,7 +1809,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="22"/>
     </row>
-    <row r="24" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
       <c r="A24" s="17"/>
       <c r="B24" s="18"/>
       <c r="C24" s="19"/>
@@ -1845,17 +1833,17 @@
       <c r="U24" s="18"/>
       <c r="V24" s="22"/>
     </row>
-    <row r="25" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A25" s="23"/>
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="24"/>
-      <c r="E25" s="26"/>
+      <c r="E25" s="21"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
-      <c r="J25" s="26"/>
+      <c r="J25" s="21"/>
       <c r="K25" s="24"/>
       <c r="L25" s="24"/>
       <c r="M25" s="24"/>
@@ -1863,23 +1851,23 @@
       <c r="O25" s="24"/>
       <c r="P25" s="24"/>
       <c r="Q25" s="24"/>
-      <c r="R25" s="27"/>
+      <c r="R25" s="26"/>
       <c r="S25" s="24"/>
       <c r="T25" s="24"/>
       <c r="U25" s="24"/>
-      <c r="V25" s="28"/>
-    </row>
-    <row r="26" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V25" s="27"/>
+    </row>
+    <row r="26" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A26" s="23"/>
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="27"/>
+      <c r="E26" s="26"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
-      <c r="J26" s="27"/>
+      <c r="J26" s="26"/>
       <c r="K26" s="24"/>
       <c r="L26" s="24"/>
       <c r="M26" s="24"/>
@@ -1887,13 +1875,13 @@
       <c r="O26" s="24"/>
       <c r="P26" s="24"/>
       <c r="Q26" s="24"/>
-      <c r="R26" s="27"/>
+      <c r="R26" s="26"/>
       <c r="S26" s="24"/>
       <c r="T26" s="24"/>
       <c r="U26" s="24"/>
-      <c r="V26" s="28"/>
-    </row>
-    <row r="27" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V26" s="27"/>
+    </row>
+    <row r="27" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
@@ -1915,9 +1903,9 @@
       <c r="S27" s="24"/>
       <c r="T27" s="24"/>
       <c r="U27" s="24"/>
-      <c r="V27" s="28"/>
-    </row>
-    <row r="28" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V27" s="27"/>
+    </row>
+    <row r="28" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A28" s="23"/>
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
@@ -1926,11 +1914,11 @@
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
-      <c r="I28" s="30"/>
+      <c r="I28" s="29"/>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
-      <c r="M28" s="30"/>
+      <c r="M28" s="29"/>
       <c r="N28" s="24"/>
       <c r="O28" s="24"/>
       <c r="P28" s="24"/>
@@ -1939,9 +1927,9 @@
       <c r="S28" s="24"/>
       <c r="T28" s="24"/>
       <c r="U28" s="24"/>
-      <c r="V28" s="28"/>
-    </row>
-    <row r="29" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V28" s="27"/>
+    </row>
+    <row r="29" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A29" s="23"/>
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
@@ -1963,9 +1951,9 @@
       <c r="S29" s="24"/>
       <c r="T29" s="24"/>
       <c r="U29" s="24"/>
-      <c r="V29" s="28"/>
-    </row>
-    <row r="30" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V29" s="27"/>
+    </row>
+    <row r="30" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A30" s="23"/>
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
@@ -1987,9 +1975,9 @@
       <c r="S30" s="24"/>
       <c r="T30" s="24"/>
       <c r="U30" s="24"/>
-      <c r="V30" s="28"/>
-    </row>
-    <row r="31" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V30" s="27"/>
+    </row>
+    <row r="31" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A31" s="23"/>
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
@@ -2011,9 +1999,9 @@
       <c r="S31" s="24"/>
       <c r="T31" s="24"/>
       <c r="U31" s="24"/>
-      <c r="V31" s="28"/>
-    </row>
-    <row r="32" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V31" s="27"/>
+    </row>
+    <row r="32" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A32" s="23"/>
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
@@ -2035,9 +2023,9 @@
       <c r="S32" s="24"/>
       <c r="T32" s="24"/>
       <c r="U32" s="24"/>
-      <c r="V32" s="28"/>
-    </row>
-    <row r="33" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V32" s="27"/>
+    </row>
+    <row r="33" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A33" s="23"/>
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
@@ -2059,9 +2047,9 @@
       <c r="S33" s="24"/>
       <c r="T33" s="24"/>
       <c r="U33" s="24"/>
-      <c r="V33" s="28"/>
-    </row>
-    <row r="34" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V33" s="27"/>
+    </row>
+    <row r="34" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
@@ -2083,9 +2071,9 @@
       <c r="S34" s="24"/>
       <c r="T34" s="24"/>
       <c r="U34" s="24"/>
-      <c r="V34" s="28"/>
-    </row>
-    <row r="35" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V34" s="27"/>
+    </row>
+    <row r="35" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
@@ -2107,9 +2095,9 @@
       <c r="S35" s="24"/>
       <c r="T35" s="24"/>
       <c r="U35" s="24"/>
-      <c r="V35" s="28"/>
-    </row>
-    <row r="36" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V35" s="27"/>
+    </row>
+    <row r="36" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
@@ -2131,9 +2119,9 @@
       <c r="S36" s="24"/>
       <c r="T36" s="24"/>
       <c r="U36" s="24"/>
-      <c r="V36" s="28"/>
-    </row>
-    <row r="37" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V36" s="27"/>
+    </row>
+    <row r="37" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
@@ -2155,9 +2143,9 @@
       <c r="S37" s="24"/>
       <c r="T37" s="24"/>
       <c r="U37" s="24"/>
-      <c r="V37" s="28"/>
-    </row>
-    <row r="38" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V37" s="27"/>
+    </row>
+    <row r="38" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A38" s="23"/>
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
@@ -2179,9 +2167,9 @@
       <c r="S38" s="24"/>
       <c r="T38" s="24"/>
       <c r="U38" s="24"/>
-      <c r="V38" s="28"/>
-    </row>
-    <row r="39" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V38" s="27"/>
+    </row>
+    <row r="39" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
       <c r="A39" s="23"/>
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
@@ -2203,55 +2191,65 @@
       <c r="S39" s="24"/>
       <c r="T39" s="24"/>
       <c r="U39" s="24"/>
-      <c r="V39" s="28"/>
-    </row>
-    <row r="40" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="31"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
-      <c r="N40" s="32"/>
-      <c r="O40" s="32"/>
-      <c r="P40" s="32"/>
-      <c r="Q40" s="32"/>
-      <c r="R40" s="32"/>
-      <c r="S40" s="32"/>
-      <c r="T40" s="32"/>
-      <c r="U40" s="32"/>
-      <c r="V40" s="34"/>
-    </row>
-    <row r="41" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
-    </row>
-    <row r="42" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="35"/>
-    </row>
-    <row r="43" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="35"/>
-    </row>
-    <row r="44" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="35"/>
-    </row>
-    <row r="45" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="35"/>
-    </row>
-    <row r="46" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="35"/>
-    </row>
-    <row r="47" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="35"/>
+      <c r="V39" s="27"/>
+    </row>
+    <row r="40" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A40" s="30"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="33"/>
+    </row>
+    <row r="41" spans="1:22" s="28" customFormat="1">
+      <c r="A41" s="34"/>
+    </row>
+    <row r="42" spans="1:22" s="28" customFormat="1">
+      <c r="A42" s="34"/>
+    </row>
+    <row r="43" spans="1:22" s="28" customFormat="1">
+      <c r="A43" s="34"/>
+    </row>
+    <row r="44" spans="1:22" s="28" customFormat="1">
+      <c r="A44" s="34"/>
+    </row>
+    <row r="45" spans="1:22" s="28" customFormat="1">
+      <c r="A45" s="34"/>
+    </row>
+    <row r="46" spans="1:22" s="28" customFormat="1">
+      <c r="A46" s="34"/>
+    </row>
+    <row r="47" spans="1:22" s="28" customFormat="1">
+      <c r="A47" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="Q6:S6"/>
     <mergeCell ref="Q1:V1"/>
     <mergeCell ref="Q2:V2"/>
     <mergeCell ref="I1:P2"/>
@@ -2268,16 +2266,6 @@
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="B5:V5"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Q6:S6"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.25" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/APLOS/POPResources/Templates/Lvr20181Bengali.xlsx
+++ b/APLOS/POPResources/Templates/Lvr20181Bengali.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Aplos.New\APLOS\POPResources\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Siddik 2018\Sadman\Compliance Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A8A106-21EC-449B-9F84-E58BC06EB4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF9247B-F3FB-46BB-8C49-D5CA1F4A27A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -180,7 +180,7 @@
     <numFmt numFmtId="164" formatCode="[$-5000445]###0;"/>
     <numFmt numFmtId="165" formatCode="[$-5000445]#,##0_);\(#,##0\)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,70 +500,70 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -577,6 +577,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -620,67 +623,76 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,13 +719,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>97194</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>272341</xdr:rowOff>
+      <xdr:rowOff>272340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>933061</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>62205</xdr:rowOff>
+      <xdr:rowOff>213829</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -730,8 +742,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5695561" y="614463"/>
-          <a:ext cx="6807459" cy="427456"/>
+          <a:off x="5569209" y="612519"/>
+          <a:ext cx="6657781" cy="582968"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1140,254 +1152,254 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.109375" style="2" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="35" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="35" customWidth="1"/>
-    <col min="4" max="6" width="9.109375" style="35" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" style="35" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" style="35" customWidth="1"/>
-    <col min="9" max="11" width="9.109375" style="35" customWidth="1"/>
-    <col min="12" max="12" width="20.6640625" style="35" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" style="36" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" style="36" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" style="36" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" style="36" customWidth="1"/>
-    <col min="17" max="19" width="9.88671875" style="35" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" style="35" customWidth="1"/>
-    <col min="21" max="21" width="14.33203125" style="35" customWidth="1"/>
-    <col min="22" max="22" width="15.88671875" style="35" customWidth="1"/>
-    <col min="23" max="16384" width="9.109375" style="35"/>
+    <col min="1" max="1" width="1.140625" style="2" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="36" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="36" customWidth="1"/>
+    <col min="4" max="6" width="9.140625" style="36" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="36" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" style="36" customWidth="1"/>
+    <col min="9" max="11" width="9.140625" style="36" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" style="36" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="37" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" style="37" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="37" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" style="37" customWidth="1"/>
+    <col min="17" max="19" width="9.85546875" style="36" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" style="36" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="36" customWidth="1"/>
+    <col min="22" max="22" width="15.85546875" style="36" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="43" customFormat="1" ht="27" customHeight="1">
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="44" t="s">
+    <row r="1" spans="1:22" s="61" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-    </row>
-    <row r="2" spans="1:22" s="2" customFormat="1" ht="25.8">
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="45" t="s">
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+    </row>
+    <row r="2" spans="1:22" s="2" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-    </row>
-    <row r="3" spans="1:22" s="39" customFormat="1" ht="24.9" customHeight="1">
-      <c r="B3" s="40" t="s">
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+    </row>
+    <row r="3" spans="1:22" s="41" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="51" t="s">
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="52"/>
-      <c r="S3" s="50" t="s">
+      <c r="R3" s="49"/>
+      <c r="S3" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-    </row>
-    <row r="4" spans="1:22" s="39" customFormat="1" ht="24.9" customHeight="1">
-      <c r="B4" s="40" t="s">
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+    </row>
+    <row r="4" spans="1:22" s="41" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="51" t="s">
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="52"/>
-      <c r="S4" s="50" t="s">
+      <c r="R4" s="49"/>
+      <c r="S4" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-    </row>
-    <row r="5" spans="1:22" s="2" customFormat="1">
-      <c r="B5" s="54" t="s">
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+    </row>
+    <row r="5" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="54"/>
-    </row>
-    <row r="6" spans="1:22" s="1" customFormat="1" ht="27" customHeight="1">
-      <c r="A6" s="37" t="s">
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="60"/>
+      <c r="R5" s="60"/>
+      <c r="S5" s="60"/>
+      <c r="T5" s="60"/>
+      <c r="U5" s="60"/>
+      <c r="V5" s="60"/>
+    </row>
+    <row r="6" spans="1:22" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="48" t="s">
+      <c r="E6" s="46"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="I6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="56"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="48" t="s">
+      <c r="J6" s="46"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="48" t="s">
+      <c r="M6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="48" t="s">
+      <c r="N6" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="48" t="s">
+      <c r="O6" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="48" t="s">
+      <c r="P6" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="55" t="s">
+      <c r="Q6" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="56"/>
-      <c r="S6" s="57"/>
-      <c r="T6" s="58" t="s">
+      <c r="R6" s="46"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="U6" s="48" t="s">
+      <c r="U6" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="V6" s="48" t="s">
+      <c r="V6" s="50" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="1" customFormat="1" ht="13.8">
-      <c r="A7" s="37"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="38" t="s">
+    <row r="7" spans="1:22" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="38"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="38" t="s">
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="J7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="38" t="s">
+      <c r="K7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="38" t="s">
+      <c r="L7" s="58"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="R7" s="38" t="s">
+      <c r="R7" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="S7" s="38" t="s">
+      <c r="S7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="T7" s="59"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-    </row>
-    <row r="8" spans="1:22" s="9" customFormat="1" ht="24.9" customHeight="1">
+      <c r="T7" s="53"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="51"/>
+    </row>
+    <row r="8" spans="1:22" s="9" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
@@ -1449,7 +1461,7 @@
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
     </row>
-    <row r="9" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="9" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
@@ -1473,7 +1485,7 @@
       <c r="U9" s="11"/>
       <c r="V9" s="15"/>
     </row>
-    <row r="10" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="10" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" s="18"/>
       <c r="C10" s="19"/>
@@ -1497,7 +1509,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="22"/>
     </row>
-    <row r="11" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="11" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="18"/>
       <c r="C11" s="19"/>
@@ -1521,7 +1533,7 @@
       <c r="U11" s="18"/>
       <c r="V11" s="22"/>
     </row>
-    <row r="12" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="12" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="18"/>
       <c r="C12" s="19"/>
@@ -1545,7 +1557,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="22"/>
     </row>
-    <row r="13" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="13" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="18"/>
       <c r="C13" s="19"/>
@@ -1569,7 +1581,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="22"/>
     </row>
-    <row r="14" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="14" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
@@ -1593,7 +1605,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="22"/>
     </row>
-    <row r="15" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="15" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
@@ -1617,7 +1629,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="22"/>
     </row>
-    <row r="16" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="16" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
@@ -1641,7 +1653,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="22"/>
     </row>
-    <row r="17" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="17" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
@@ -1665,7 +1677,7 @@
       <c r="U17" s="18"/>
       <c r="V17" s="22"/>
     </row>
-    <row r="18" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="18" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="18"/>
       <c r="C18" s="19"/>
@@ -1689,7 +1701,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="22"/>
     </row>
-    <row r="19" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="19" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="18"/>
       <c r="C19" s="19"/>
@@ -1713,7 +1725,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="22"/>
     </row>
-    <row r="20" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="20" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
@@ -1737,7 +1749,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="22"/>
     </row>
-    <row r="21" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="21" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
@@ -1761,7 +1773,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="22"/>
     </row>
-    <row r="22" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="22" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
@@ -1785,7 +1797,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="22"/>
     </row>
-    <row r="23" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="23" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
@@ -1809,7 +1821,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="22"/>
     </row>
-    <row r="24" spans="1:22" s="16" customFormat="1" ht="24.9" customHeight="1">
+    <row r="24" spans="1:22" s="16" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="18"/>
       <c r="C24" s="19"/>
@@ -1833,17 +1845,17 @@
       <c r="U24" s="18"/>
       <c r="V24" s="22"/>
     </row>
-    <row r="25" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+    <row r="25" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="24"/>
-      <c r="E25" s="21"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
-      <c r="J25" s="21"/>
+      <c r="J25" s="26"/>
       <c r="K25" s="24"/>
       <c r="L25" s="24"/>
       <c r="M25" s="24"/>
@@ -1851,23 +1863,23 @@
       <c r="O25" s="24"/>
       <c r="P25" s="24"/>
       <c r="Q25" s="24"/>
-      <c r="R25" s="26"/>
+      <c r="R25" s="27"/>
       <c r="S25" s="24"/>
       <c r="T25" s="24"/>
       <c r="U25" s="24"/>
-      <c r="V25" s="27"/>
-    </row>
-    <row r="26" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V25" s="28"/>
+    </row>
+    <row r="26" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="23"/>
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="26"/>
+      <c r="E26" s="27"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
-      <c r="J26" s="26"/>
+      <c r="J26" s="27"/>
       <c r="K26" s="24"/>
       <c r="L26" s="24"/>
       <c r="M26" s="24"/>
@@ -1875,13 +1887,13 @@
       <c r="O26" s="24"/>
       <c r="P26" s="24"/>
       <c r="Q26" s="24"/>
-      <c r="R26" s="26"/>
+      <c r="R26" s="27"/>
       <c r="S26" s="24"/>
       <c r="T26" s="24"/>
       <c r="U26" s="24"/>
-      <c r="V26" s="27"/>
-    </row>
-    <row r="27" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V26" s="28"/>
+    </row>
+    <row r="27" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="23"/>
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
@@ -1903,9 +1915,9 @@
       <c r="S27" s="24"/>
       <c r="T27" s="24"/>
       <c r="U27" s="24"/>
-      <c r="V27" s="27"/>
-    </row>
-    <row r="28" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V27" s="28"/>
+    </row>
+    <row r="28" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="23"/>
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
@@ -1914,11 +1926,11 @@
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
-      <c r="I28" s="29"/>
+      <c r="I28" s="30"/>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
-      <c r="M28" s="29"/>
+      <c r="M28" s="30"/>
       <c r="N28" s="24"/>
       <c r="O28" s="24"/>
       <c r="P28" s="24"/>
@@ -1927,9 +1939,9 @@
       <c r="S28" s="24"/>
       <c r="T28" s="24"/>
       <c r="U28" s="24"/>
-      <c r="V28" s="27"/>
-    </row>
-    <row r="29" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V28" s="28"/>
+    </row>
+    <row r="29" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="23"/>
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
@@ -1951,9 +1963,9 @@
       <c r="S29" s="24"/>
       <c r="T29" s="24"/>
       <c r="U29" s="24"/>
-      <c r="V29" s="27"/>
-    </row>
-    <row r="30" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V29" s="28"/>
+    </row>
+    <row r="30" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23"/>
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
@@ -1975,9 +1987,9 @@
       <c r="S30" s="24"/>
       <c r="T30" s="24"/>
       <c r="U30" s="24"/>
-      <c r="V30" s="27"/>
-    </row>
-    <row r="31" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V30" s="28"/>
+    </row>
+    <row r="31" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="23"/>
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
@@ -1999,9 +2011,9 @@
       <c r="S31" s="24"/>
       <c r="T31" s="24"/>
       <c r="U31" s="24"/>
-      <c r="V31" s="27"/>
-    </row>
-    <row r="32" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V31" s="28"/>
+    </row>
+    <row r="32" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="23"/>
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
@@ -2023,9 +2035,9 @@
       <c r="S32" s="24"/>
       <c r="T32" s="24"/>
       <c r="U32" s="24"/>
-      <c r="V32" s="27"/>
-    </row>
-    <row r="33" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V32" s="28"/>
+    </row>
+    <row r="33" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="23"/>
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
@@ -2047,9 +2059,9 @@
       <c r="S33" s="24"/>
       <c r="T33" s="24"/>
       <c r="U33" s="24"/>
-      <c r="V33" s="27"/>
-    </row>
-    <row r="34" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V33" s="28"/>
+    </row>
+    <row r="34" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
@@ -2071,9 +2083,9 @@
       <c r="S34" s="24"/>
       <c r="T34" s="24"/>
       <c r="U34" s="24"/>
-      <c r="V34" s="27"/>
-    </row>
-    <row r="35" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V34" s="28"/>
+    </row>
+    <row r="35" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
@@ -2095,9 +2107,9 @@
       <c r="S35" s="24"/>
       <c r="T35" s="24"/>
       <c r="U35" s="24"/>
-      <c r="V35" s="27"/>
-    </row>
-    <row r="36" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V35" s="28"/>
+    </row>
+    <row r="36" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
@@ -2119,9 +2131,9 @@
       <c r="S36" s="24"/>
       <c r="T36" s="24"/>
       <c r="U36" s="24"/>
-      <c r="V36" s="27"/>
-    </row>
-    <row r="37" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V36" s="28"/>
+    </row>
+    <row r="37" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
@@ -2143,9 +2155,9 @@
       <c r="S37" s="24"/>
       <c r="T37" s="24"/>
       <c r="U37" s="24"/>
-      <c r="V37" s="27"/>
-    </row>
-    <row r="38" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V37" s="28"/>
+    </row>
+    <row r="38" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
@@ -2167,9 +2179,9 @@
       <c r="S38" s="24"/>
       <c r="T38" s="24"/>
       <c r="U38" s="24"/>
-      <c r="V38" s="27"/>
-    </row>
-    <row r="39" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
+      <c r="V38" s="28"/>
+    </row>
+    <row r="39" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
@@ -2191,65 +2203,55 @@
       <c r="S39" s="24"/>
       <c r="T39" s="24"/>
       <c r="U39" s="24"/>
-      <c r="V39" s="27"/>
-    </row>
-    <row r="40" spans="1:22" s="28" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A40" s="30"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="31"/>
-      <c r="S40" s="31"/>
-      <c r="T40" s="31"/>
-      <c r="U40" s="31"/>
-      <c r="V40" s="33"/>
-    </row>
-    <row r="41" spans="1:22" s="28" customFormat="1">
-      <c r="A41" s="34"/>
-    </row>
-    <row r="42" spans="1:22" s="28" customFormat="1">
-      <c r="A42" s="34"/>
-    </row>
-    <row r="43" spans="1:22" s="28" customFormat="1">
-      <c r="A43" s="34"/>
-    </row>
-    <row r="44" spans="1:22" s="28" customFormat="1">
-      <c r="A44" s="34"/>
-    </row>
-    <row r="45" spans="1:22" s="28" customFormat="1">
-      <c r="A45" s="34"/>
-    </row>
-    <row r="46" spans="1:22" s="28" customFormat="1">
-      <c r="A46" s="34"/>
-    </row>
-    <row r="47" spans="1:22" s="28" customFormat="1">
-      <c r="A47" s="34"/>
+      <c r="V39" s="28"/>
+    </row>
+    <row r="40" spans="1:22" s="29" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="31"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="32"/>
+      <c r="V40" s="34"/>
+    </row>
+    <row r="41" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="35"/>
+    </row>
+    <row r="42" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="35"/>
+    </row>
+    <row r="43" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="35"/>
+    </row>
+    <row r="44" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="35"/>
+    </row>
+    <row r="45" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="35"/>
+    </row>
+    <row r="46" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="35"/>
+    </row>
+    <row r="47" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Q6:S6"/>
     <mergeCell ref="Q1:V1"/>
     <mergeCell ref="Q2:V2"/>
     <mergeCell ref="I1:P2"/>
@@ -2266,6 +2268,16 @@
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="B5:V5"/>
     <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="Q6:S6"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.25" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
